--- a/Journal-de-Travail_BorminKiril.xlsx
+++ b/Journal-de-Travail_BorminKiril.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\347-docker-swarm-wordpress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57F2BC2-75D8-413C-8FC9-7E8C2BDBF099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE20905-E799-4FD8-8CA1-8DFC3AE6D443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="4185" yWindow="2715" windowWidth="14445" windowHeight="8565" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -149,6 +149,21 @@
   </si>
   <si>
     <t>Installation de docker sur toutes les machines</t>
+  </si>
+  <si>
+    <t>Initialisation du cluster Swarm sur le manager et connexion des deux workers</t>
+  </si>
+  <si>
+    <t>Création des réseaux overlay (frontend, backend) et des Docker Secrets</t>
+  </si>
+  <si>
+    <t>Config du nginx et docker compose</t>
+  </si>
+  <si>
+    <t>Déploiement de la stack WordPress et résolution de l'erreur de build MariaDB</t>
+  </si>
+  <si>
+    <t>L'image mariadb 12.0.1 n'existe pas sur Docker Hub, utilisation du tag 11.4</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1174,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>290</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4255,7 +4270,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>2 heures 5 minutes</v>
+        <v>4 heures 50 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4270,15 +4285,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>125</v>
+        <v>290</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4422,15 +4437,23 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="63" t="str">
+      <c r="A11" s="63">
         <f>IF(ISBLANK(B11),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B11))</f>
-        <v/>
-      </c>
-      <c r="B11" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="B11" s="34">
+        <v>46267</v>
+      </c>
       <c r="C11" s="35"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="23"/>
+      <c r="D11" s="36">
+        <v>35</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>36</v>
+      </c>
       <c r="G11" s="40"/>
       <c r="M11" t="s">
         <v>17</v>
@@ -4443,15 +4466,23 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="62" t="str">
+      <c r="A12" s="62">
         <f>IF(ISBLANK(B12),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B12))</f>
-        <v/>
-      </c>
-      <c r="B12" s="30"/>
+        <v>36</v>
+      </c>
+      <c r="B12" s="30">
+        <v>46267</v>
+      </c>
       <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="23"/>
+      <c r="D12" s="32">
+        <v>25</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>37</v>
+      </c>
       <c r="G12" s="39"/>
       <c r="M12" t="s">
         <v>18</v>
@@ -4464,15 +4495,23 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="str">
+      <c r="A13" s="63">
         <f>IF(ISBLANK(B13),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B13))</f>
-        <v/>
-      </c>
-      <c r="B13" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="B13" s="34">
+        <v>46267</v>
+      </c>
       <c r="C13" s="35"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="23"/>
+      <c r="D13" s="36">
+        <v>45</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="G13" s="40"/>
       <c r="N13">
         <v>6</v>
@@ -4482,16 +4521,26 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="62" t="str">
+      <c r="A14" s="62">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
-        <v/>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
+        <v>36</v>
+      </c>
+      <c r="B14" s="30">
+        <v>46267</v>
+      </c>
+      <c r="C14" s="31">
+        <v>1</v>
+      </c>
       <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="39"/>
+      <c r="E14" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>40</v>
+      </c>
       <c r="N14">
         <v>7</v>
       </c>
@@ -10904,15 +10953,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>290</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10920,7 +10969,7 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>2 h 05 min</v>
+        <v>4 h 50 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
@@ -11050,26 +11099,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>125</v>
+        <v>290</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>2 h 05 min</v>
+        <v>4 h 50 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>2.3148148148148147E-2</v>
+        <v>5.3703703703703705E-2</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>29</v>
@@ -11108,26 +11157,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="62349bcdb43c26c508700efba1cb50b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e5d6db3f342a25e0e30f4a2965162e1" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11316,10 +11345,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1424D28F-D6A9-45ED-AED5-A0D744400EE5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11342,20 +11402,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1424D28F-D6A9-45ED-AED5-A0D744400EE5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>